--- a/pages/shp/uploads/05-05-2026 - 05-05-2026 (1).xlsx
+++ b/pages/shp/uploads/05-05-2026 - 05-05-2026 (1).xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="332">
   <si>
     <t>NOMOR AJU</t>
   </si>
@@ -347,522 +347,572 @@
     <t>FLAG PROPORSIONAL NETTO</t>
   </si>
   <si>
-    <t>000033NIW34520260505000009</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>160200</t>
+    <t>000262NIW34520260505000445</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>050500</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>BANDUNG</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>YUS YULIUS</t>
+  </si>
+  <si>
+    <t>EXIM MANAGER</t>
+  </si>
+  <si>
+    <t>IDR</t>
+  </si>
+  <si>
+    <t>013916</t>
+  </si>
+  <si>
+    <t>000262NIW34520260505000444</t>
+  </si>
+  <si>
+    <t>013852</t>
+  </si>
+  <si>
+    <t>KODE FASILITAS TARIF</t>
+  </si>
+  <si>
+    <t>KODE JENIS PUNGUTAN</t>
+  </si>
+  <si>
+    <t>NILAI PUNGUTAN</t>
+  </si>
+  <si>
+    <t>NPWP BILLING</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>PPN</t>
+  </si>
+  <si>
+    <t>PPH</t>
+  </si>
+  <si>
+    <t>BM</t>
+  </si>
+  <si>
+    <t>BMTP</t>
+  </si>
+  <si>
+    <t>SERI</t>
+  </si>
+  <si>
+    <t>KODE ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS IDENTITAS</t>
+  </si>
+  <si>
+    <t>NOMOR IDENTITAS</t>
+  </si>
+  <si>
+    <t>NAMA ENTITAS</t>
+  </si>
+  <si>
+    <t>ALAMAT ENTITAS</t>
+  </si>
+  <si>
+    <t>NIB ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS API</t>
+  </si>
+  <si>
+    <t>KODE STATUS</t>
+  </si>
+  <si>
+    <t>NOMOR IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>TANGGAL IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE NEGARA</t>
+  </si>
+  <si>
+    <t>NIPER ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE KATEGORI KONSOLIDATOR</t>
+  </si>
+  <si>
+    <t>KODE AFILIASI</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>0745406926444000000000</t>
+  </si>
+  <si>
+    <t>NIRWANA ALABARE GARMENT</t>
+  </si>
+  <si>
+    <t>JALAN RAYA RANCAEKAEK MAJALAYA NO.289 001/007</t>
+  </si>
+  <si>
+    <t>0220103231143</t>
+  </si>
+  <si>
+    <t>16/MK/WBC.09/2026</t>
+  </si>
+  <si>
+    <t>01-20-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>0025445305441000000000</t>
+  </si>
+  <si>
+    <t>GUNAJAYA SANTOSA</t>
+  </si>
+  <si>
+    <t>JALAN RANCAJIGANG NO.110 RT.004 RW.010, PADAMULYA, MAJALAYA, KABUPATEN BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>LAINNYA</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>JL RAYA RANCAEKEK MAJALAYA NO.289 RT.002 RW.007, SOLOKANJERUK, SOLOKANJERUK, KABUPATEN BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>0030509350444000000000</t>
+  </si>
+  <si>
+    <t>SOLJER ABADI</t>
+  </si>
+  <si>
+    <t>JL. RAYA RANCAEKEK - MAJALAYA NO.289 , SOLOKANJERUK RT.000 RW.000, SOLOKANJERUK, SOLOKANJERUK, KABUPATEN BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>NOMOR DOKUMEN</t>
+  </si>
+  <si>
+    <t>TANGGAL DOKUMEN</t>
+  </si>
+  <si>
+    <t>KODE FASILITAS</t>
+  </si>
+  <si>
+    <t>KODE IJIN</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>1411/TPB-SK.01/KBC.0903/2026</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>085/NAG/KK/IV/2026</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>997</t>
+  </si>
+  <si>
+    <t>CBD 2026 04 898 01 10077</t>
+  </si>
+  <si>
+    <t>994</t>
+  </si>
+  <si>
+    <t>001159/BPJ/CB/2026</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>GS-00358/05/26,GS-00359/05/26</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>007861</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>008444</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>1745/TPB-SK.01/KBC.0903/2026</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>100/NAG/KK/IV/2026</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>CBD 2026 04 898 01 11632</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>001447/BPJ/CB/2026</t>
+  </si>
+  <si>
+    <t>260525789</t>
+  </si>
+  <si>
+    <t>009387</t>
+  </si>
+  <si>
+    <t>KODE CARA ANGKUT</t>
+  </si>
+  <si>
+    <t>NAMA PENGANGKUT</t>
+  </si>
+  <si>
+    <t>NOMOR PENGANGKUT</t>
+  </si>
+  <si>
+    <t>KODE BENDERA</t>
+  </si>
+  <si>
+    <t>CALL SIGN</t>
+  </si>
+  <si>
+    <t>FLAG ANGKUT PLB</t>
+  </si>
+  <si>
+    <t>CARA PENGANGKUTAN LAINNYA</t>
+  </si>
+  <si>
+    <t>KODE KEMASAN</t>
+  </si>
+  <si>
+    <t>JUMLAH KEMASAN</t>
+  </si>
+  <si>
+    <t>MEREK</t>
+  </si>
+  <si>
+    <t>NOMOR SEGEL</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>NOMOR KONTINER</t>
+  </si>
+  <si>
+    <t>KODE UKURAN KONTAINER</t>
+  </si>
+  <si>
+    <t>KODE JENIS KONTAINER</t>
+  </si>
+  <si>
+    <t>KODE TIPE KONTAINER</t>
+  </si>
+  <si>
+    <t>SERI BARANG</t>
+  </si>
+  <si>
+    <t>HS</t>
+  </si>
+  <si>
+    <t>KODE BARANG</t>
+  </si>
+  <si>
+    <t>URAIAN</t>
+  </si>
+  <si>
+    <t>TIPE</t>
+  </si>
+  <si>
+    <t>UKURAN</t>
+  </si>
+  <si>
+    <t>SPESIFIKASI LAIN</t>
+  </si>
+  <si>
+    <t>KODE SATUAN</t>
+  </si>
+  <si>
+    <t>JUMLAH SATUAN</t>
+  </si>
+  <si>
+    <t>KODE DOKUMEN ASAL</t>
+  </si>
+  <si>
+    <t>KODE KANTOR ASAL</t>
+  </si>
+  <si>
+    <t>NOMOR DAFTAR ASAL</t>
+  </si>
+  <si>
+    <t>TANGGAL DAFTAR ASAL</t>
+  </si>
+  <si>
+    <t>NOMOR AJU ASAL</t>
+  </si>
+  <si>
+    <t>SERI BARANG ASAL</t>
+  </si>
+  <si>
+    <t>SALDO AWAL</t>
+  </si>
+  <si>
+    <t>SALDO AKHIR</t>
+  </si>
+  <si>
+    <t>JUMLAH REALISASI</t>
+  </si>
+  <si>
+    <t>CIF RUPIAH</t>
+  </si>
+  <si>
+    <t>NILAI TAMBAH</t>
+  </si>
+  <si>
+    <t>DISKON</t>
+  </si>
+  <si>
+    <t>HARGA PENYERAHAN</t>
+  </si>
+  <si>
+    <t>HARGA PEROLEHAN</t>
+  </si>
+  <si>
+    <t>HARGA SATUAN</t>
+  </si>
+  <si>
+    <t>HARGA EKSPOR</t>
+  </si>
+  <si>
+    <t>HARGA PATOKAN</t>
+  </si>
+  <si>
+    <t>NILAI DANA SAWIT</t>
+  </si>
+  <si>
+    <t>NILAI DEVISA</t>
+  </si>
+  <si>
+    <t>PERSENTASE IMPOR</t>
+  </si>
+  <si>
+    <t>KODE ASAL BARANG</t>
+  </si>
+  <si>
+    <t>KODE GUNA BARANG</t>
+  </si>
+  <si>
+    <t>JATUH TEMPO ROYALTI</t>
+  </si>
+  <si>
+    <t>KODE KATEGORI BARANG</t>
+  </si>
+  <si>
+    <t>KODE KONDISI BARANG</t>
+  </si>
+  <si>
+    <t>KODE NEGARA ASAL</t>
+  </si>
+  <si>
+    <t>KODE PERHITUNGAN</t>
+  </si>
+  <si>
+    <t>PERNYATAAN LARTAS</t>
+  </si>
+  <si>
+    <t>FLAG 4 TAHUN</t>
+  </si>
+  <si>
+    <t>SERI IZIN</t>
+  </si>
+  <si>
+    <t>TAHUN PEMBUATAN</t>
+  </si>
+  <si>
+    <t>KAPASITAS SILINDER</t>
+  </si>
+  <si>
+    <t>KODE BKC</t>
+  </si>
+  <si>
+    <t>KODE KOMODITI BKC</t>
+  </si>
+  <si>
+    <t>KODE SUB KOMODITI BKC</t>
+  </si>
+  <si>
+    <t>FLAG TIS</t>
+  </si>
+  <si>
+    <t>ISI PER KEMASAN</t>
+  </si>
+  <si>
+    <t>JUMLAH DILEKATKAN</t>
+  </si>
+  <si>
+    <t>JUMLAH PITA CUKAI</t>
+  </si>
+  <si>
+    <t>HJE CUKAI</t>
+  </si>
+  <si>
+    <t>TARIF CUKAI</t>
+  </si>
+  <si>
+    <t>METODE PENENTUAN NILAI</t>
+  </si>
+  <si>
+    <t>ALASAN METODE PENENTUAN NILAI</t>
+  </si>
+  <si>
+    <t>STATEMENT PERBEDAAN HARGA</t>
+  </si>
+  <si>
+    <t>54078200</t>
+  </si>
+  <si>
+    <t>KN_2</t>
+  </si>
+  <si>
+    <t>FABRIC HASIL CELUP ( FABRIC 90% MODAL 10% SPANDEX SINGLE JERSEY )</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>KGM</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>60062200</t>
+  </si>
+  <si>
+    <t>KN_16</t>
+  </si>
+  <si>
+    <t>FABRIC HASIL KNITTING (FABRIC 100% COTTON B2886 RIB 1X1 )</t>
+  </si>
+  <si>
+    <t>KODE PUNGUTAN</t>
+  </si>
+  <si>
+    <t>KODE TARIF</t>
+  </si>
+  <si>
+    <t>TARIF</t>
+  </si>
+  <si>
+    <t>TARIF FASILITAS</t>
+  </si>
+  <si>
+    <t>NILAI BAYAR</t>
+  </si>
+  <si>
+    <t>NILAI FASILITAS</t>
+  </si>
+  <si>
+    <t>NILAI SUDAH DILUNASI</t>
+  </si>
+  <si>
+    <t>FLAG BMT SEMENTARA</t>
+  </si>
+  <si>
+    <t>KODE KOMODITI CUKAI</t>
+  </si>
+  <si>
+    <t>KODE SUB KOMODITI CUKAI</t>
+  </si>
+  <si>
+    <t>FLAG PELEKATAN</t>
+  </si>
+  <si>
+    <t>SERI DOKUMEN</t>
+  </si>
+  <si>
+    <t>SERI ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE</t>
+  </si>
+  <si>
+    <t>KODE VD</t>
+  </si>
+  <si>
+    <t>JATUH TEMPO</t>
+  </si>
+  <si>
+    <t>SERI BAHAN BAKU</t>
+  </si>
+  <si>
+    <t>KODE ASAL BAHAN BAKU</t>
+  </si>
+  <si>
+    <t>VALUTA</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>DW03</t>
-  </si>
-  <si>
-    <t>3204</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
-    <t>COBUN</t>
-  </si>
-  <si>
-    <t>IDTPP</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>DN</t>
-  </si>
-  <si>
-    <t>BANDUNG</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>YUS YULIUS</t>
-  </si>
-  <si>
-    <t>MANAGER EXIM</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>040300</t>
-  </si>
-  <si>
-    <t>104329</t>
-  </si>
-  <si>
-    <t>KODE FASILITAS TARIF</t>
-  </si>
-  <si>
-    <t>KODE JENIS PUNGUTAN</t>
-  </si>
-  <si>
-    <t>NILAI PUNGUTAN</t>
-  </si>
-  <si>
-    <t>NPWP BILLING</t>
-  </si>
-  <si>
-    <t>SERI</t>
-  </si>
-  <si>
-    <t>KODE ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS IDENTITAS</t>
-  </si>
-  <si>
-    <t>NOMOR IDENTITAS</t>
-  </si>
-  <si>
-    <t>NAMA ENTITAS</t>
-  </si>
-  <si>
-    <t>ALAMAT ENTITAS</t>
-  </si>
-  <si>
-    <t>NIB ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS API</t>
-  </si>
-  <si>
-    <t>KODE STATUS</t>
-  </si>
-  <si>
-    <t>NOMOR IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>TANGGAL IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE NEGARA</t>
-  </si>
-  <si>
-    <t>NIPER ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE KATEGORI KONSOLIDATOR</t>
-  </si>
-  <si>
-    <t>KODE AFILIASI</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>FORUS COLOMBIA SAS/1038786</t>
-  </si>
-  <si>
-    <t>EDIF. PARALELO 108 TORRE 3 PISO 7
-NIT:900.136.788-4 AV CRA 45 #108-27
-BOGOTA, 111111, COLOMBIA</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>0745406926444000000000</t>
-  </si>
-  <si>
-    <t>PT NIRWANA ALABARE GARMENT</t>
-  </si>
-  <si>
-    <t>JL RAYA RANCAEKEK MAJALAYA NO 289
-DESA SOLOKAN JERUK KECAMATAN SOLOKAN JERUK
-KABUPATEN BANDUNG</t>
-  </si>
-  <si>
-    <t>0220103231143</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>0010720829058000000000</t>
-  </si>
-  <si>
-    <t>MAERSK LOGISTICS INDONESIA</t>
-  </si>
-  <si>
-    <t>GEDUNG INTERNATIONAL FINANCIAL CENTRE TOWER 2 LT 40-41 JL JENDERAL SUDIRMAN KAV 22-23 RT.000 RW.000, KARET, SETIABUDI, KOTA ADMINISTRASI JAKARTA SELATAN, DAERAH KHUSUS IBUKOTA JAKARTA</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>LAINNYA</t>
-  </si>
-  <si>
-    <t>175/MK/WBC.08/2026</t>
-  </si>
-  <si>
-    <t>03-13-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>NIRWANA ALABARE GARMENT</t>
-  </si>
-  <si>
-    <t>JL RAYA RANCAEKEK MAJALAYA NO.289 RT.002 RW.007, SOLOKANJERUK, SOLOKANJERUK, KABUPATEN BANDUNG, JAWA BARAT</t>
-  </si>
-  <si>
-    <t>NOMOR DOKUMEN</t>
-  </si>
-  <si>
-    <t>TANGGAL DOKUMEN</t>
-  </si>
-  <si>
-    <t>KODE FASILITAS</t>
-  </si>
-  <si>
-    <t>KODE IJIN</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>TFKC26050029</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>920</t>
-  </si>
-  <si>
-    <t>16/MK/WBC.09/2026</t>
-  </si>
-  <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
-    <t>KODE CARA ANGKUT</t>
-  </si>
-  <si>
-    <t>NAMA PENGANGKUT</t>
-  </si>
-  <si>
-    <t>NOMOR PENGANGKUT</t>
-  </si>
-  <si>
-    <t>KODE BENDERA</t>
-  </si>
-  <si>
-    <t>CALL SIGN</t>
-  </si>
-  <si>
-    <t>FLAG ANGKUT PLB</t>
-  </si>
-  <si>
-    <t>CARA PENGANGKUTAN LAINNYA</t>
-  </si>
-  <si>
-    <t>CNC PANTHER</t>
-  </si>
-  <si>
-    <t>0K81ON</t>
-  </si>
-  <si>
-    <t>KODE KEMASAN</t>
-  </si>
-  <si>
-    <t>JUMLAH KEMASAN</t>
-  </si>
-  <si>
-    <t>MEREK</t>
-  </si>
-  <si>
-    <t>NOMOR SEGEL</t>
-  </si>
-  <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>COLUMBIA</t>
-  </si>
-  <si>
-    <t>NOMOR KONTINER</t>
-  </si>
-  <si>
-    <t>KODE UKURAN KONTAINER</t>
-  </si>
-  <si>
-    <t>KODE JENIS KONTAINER</t>
-  </si>
-  <si>
-    <t>KODE TIPE KONTAINER</t>
-  </si>
-  <si>
-    <t>SERI BARANG</t>
-  </si>
-  <si>
-    <t>HS</t>
-  </si>
-  <si>
-    <t>KODE BARANG</t>
-  </si>
-  <si>
-    <t>URAIAN</t>
-  </si>
-  <si>
-    <t>TIPE</t>
-  </si>
-  <si>
-    <t>UKURAN</t>
-  </si>
-  <si>
-    <t>SPESIFIKASI LAIN</t>
-  </si>
-  <si>
-    <t>KODE SATUAN</t>
-  </si>
-  <si>
-    <t>JUMLAH SATUAN</t>
-  </si>
-  <si>
-    <t>KODE DOKUMEN ASAL</t>
-  </si>
-  <si>
-    <t>KODE KANTOR ASAL</t>
-  </si>
-  <si>
-    <t>NOMOR DAFTAR ASAL</t>
-  </si>
-  <si>
-    <t>TANGGAL DAFTAR ASAL</t>
-  </si>
-  <si>
-    <t>NOMOR AJU ASAL</t>
-  </si>
-  <si>
-    <t>SERI BARANG ASAL</t>
-  </si>
-  <si>
-    <t>SALDO AWAL</t>
-  </si>
-  <si>
-    <t>SALDO AKHIR</t>
-  </si>
-  <si>
-    <t>JUMLAH REALISASI</t>
-  </si>
-  <si>
-    <t>CIF RUPIAH</t>
-  </si>
-  <si>
-    <t>NILAI TAMBAH</t>
-  </si>
-  <si>
-    <t>DISKON</t>
-  </si>
-  <si>
-    <t>HARGA PENYERAHAN</t>
-  </si>
-  <si>
-    <t>HARGA PEROLEHAN</t>
-  </si>
-  <si>
-    <t>HARGA SATUAN</t>
-  </si>
-  <si>
-    <t>HARGA EKSPOR</t>
-  </si>
-  <si>
-    <t>HARGA PATOKAN</t>
-  </si>
-  <si>
-    <t>NILAI DANA SAWIT</t>
-  </si>
-  <si>
-    <t>NILAI DEVISA</t>
-  </si>
-  <si>
-    <t>PERSENTASE IMPOR</t>
-  </si>
-  <si>
-    <t>KODE ASAL BARANG</t>
-  </si>
-  <si>
-    <t>KODE GUNA BARANG</t>
-  </si>
-  <si>
-    <t>JATUH TEMPO ROYALTI</t>
-  </si>
-  <si>
-    <t>KODE KATEGORI BARANG</t>
-  </si>
-  <si>
-    <t>KODE KONDISI BARANG</t>
-  </si>
-  <si>
-    <t>KODE NEGARA ASAL</t>
-  </si>
-  <si>
-    <t>KODE PERHITUNGAN</t>
-  </si>
-  <si>
-    <t>PERNYATAAN LARTAS</t>
-  </si>
-  <si>
-    <t>FLAG 4 TAHUN</t>
-  </si>
-  <si>
-    <t>SERI IZIN</t>
-  </si>
-  <si>
-    <t>TAHUN PEMBUATAN</t>
-  </si>
-  <si>
-    <t>KAPASITAS SILINDER</t>
-  </si>
-  <si>
-    <t>KODE BKC</t>
-  </si>
-  <si>
-    <t>KODE KOMODITI BKC</t>
-  </si>
-  <si>
-    <t>KODE SUB KOMODITI BKC</t>
-  </si>
-  <si>
-    <t>FLAG TIS</t>
-  </si>
-  <si>
-    <t>ISI PER KEMASAN</t>
-  </si>
-  <si>
-    <t>JUMLAH DILEKATKAN</t>
-  </si>
-  <si>
-    <t>JUMLAH PITA CUKAI</t>
-  </si>
-  <si>
-    <t>HJE CUKAI</t>
-  </si>
-  <si>
-    <t>TARIF CUKAI</t>
-  </si>
-  <si>
-    <t>METODE PENENTUAN NILAI</t>
-  </si>
-  <si>
-    <t>ALASAN METODE PENENTUAN NILAI</t>
-  </si>
-  <si>
-    <t>STATEMENT PERBEDAAN HARGA</t>
-  </si>
-  <si>
-    <t>61052010</t>
-  </si>
-  <si>
-    <t>CLB/0126/006</t>
-  </si>
-  <si>
-    <t>POLO SHIRT (UTILIZER™ POLO)
-PO NO : 4550360224
-STYLE : AM0126</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>PCE</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>POLO SHIRT (UTILIZER™ POLO)
-PO NO : 4550360256
-STYLE : AM0126</t>
-  </si>
-  <si>
-    <t>KODE PUNGUTAN</t>
-  </si>
-  <si>
-    <t>KODE TARIF</t>
-  </si>
-  <si>
-    <t>TARIF</t>
-  </si>
-  <si>
-    <t>TARIF FASILITAS</t>
-  </si>
-  <si>
-    <t>NILAI BAYAR</t>
-  </si>
-  <si>
-    <t>NILAI FASILITAS</t>
-  </si>
-  <si>
-    <t>NILAI SUDAH DILUNASI</t>
-  </si>
-  <si>
-    <t>FLAG BMT SEMENTARA</t>
-  </si>
-  <si>
-    <t>KODE KOMODITI CUKAI</t>
-  </si>
-  <si>
-    <t>KODE SUB KOMODITI CUKAI</t>
-  </si>
-  <si>
-    <t>FLAG PELEKATAN</t>
-  </si>
-  <si>
-    <t>SERI DOKUMEN</t>
-  </si>
-  <si>
-    <t>SERI ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE</t>
-  </si>
-  <si>
-    <t>KODE VD</t>
-  </si>
-  <si>
-    <t>JATUH TEMPO</t>
-  </si>
-  <si>
-    <t>SERI BAHAN BAKU</t>
-  </si>
-  <si>
-    <t>KODE ASAL BAHAN BAKU</t>
-  </si>
-  <si>
-    <t>VALUTA</t>
+    <t>FABRIC UNTUK DI CELUP ( FABRIC 90% MODAL 10% SPANDEX SINGLE JERSEY )</t>
+  </si>
+  <si>
+    <t>04-10-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>52052400</t>
+  </si>
+  <si>
+    <t>YARN UNTUK DI KNITTING ( 100% COTTON
+TOP DYED ( COMBED 40S RING SPUN B2886 )</t>
+  </si>
+  <si>
+    <t>04-27-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>KODE_ASAL_BAHAN_BAKU</t>
@@ -892,15 +942,21 @@
     <t>TANGGAL BPJ</t>
   </si>
   <si>
+    <t>04-07-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>JAMKRIDA JAKARTA</t>
+  </si>
+  <si>
+    <t>07-05-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>07-22-2026 00:00:00</t>
+  </si>
+  <si>
     <t>NAMA</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>BANK BCA</t>
-  </si>
-  <si>
     <t>JENIS NILAI</t>
   </si>
   <si>
@@ -967,10 +1023,13 @@
     <t>TANGGAL RESPON</t>
   </si>
   <si>
-    <t>3303</t>
-  </si>
-  <si>
-    <t>102985/KBC.0802/2026</t>
+    <t>26202</t>
+  </si>
+  <si>
+    <t>013916/KBC.0903/2026</t>
+  </si>
+  <si>
+    <t>013852/KBC.0903/2026</t>
   </si>
 </sst>
 </file>
@@ -1098,6 +1157,7 @@
     <col min="67" max="67" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="70" max="70" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="71" max="71" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="73" max="73" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="74" max="74" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="76" max="76" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="77" max="77" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1463,136 +1523,165 @@
       <c r="C2" t="s">
         <v>106</v>
       </c>
-      <c r="I2" t="s">
+      <c r="M2" t="s">
         <v>107</v>
       </c>
-      <c r="L2" t="s">
+      <c r="BK2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.2045358325E8</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>1590.9</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>1478.0</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>108</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>109</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>110</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>111</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>109</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M3" t="s">
         <v>107</v>
       </c>
-      <c r="P2" t="s">
+      <c r="BK3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>3117632.49</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE3" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="CF3" t="s">
         <v>109</v>
       </c>
-      <c r="S2" t="s">
+      <c r="CG3" t="s">
         <v>110</v>
       </c>
-      <c r="W2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE2" t="s">
+      <c r="CH3" t="s">
         <v>111</v>
       </c>
-      <c r="AF2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AH2" t="s">
+      <c r="CI3" t="s">
         <v>112</v>
       </c>
-      <c r="AN2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AW2" t="s">
+      <c r="CP3" t="s">
         <v>115</v>
       </c>
-      <c r="AX2" t="s">
-        <v>116</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>117</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>117</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1601.36</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1601.36</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>17217.0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>304.33</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>266.95</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>119</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>120</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>121</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CI2" t="s">
-        <v>123</v>
-      </c>
-      <c r="CJ2" t="s">
-        <v>65</v>
-      </c>
-      <c r="CO2" t="s">
-        <v>124</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>125</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>120</v>
-      </c>
-      <c r="CT2" t="n">
+      <c r="CQ3" t="s">
+        <v>109</v>
+      </c>
+      <c r="CT3" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -1614,7 +1703,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1625,13 +1714,35 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1662,10 +1773,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -1695,13 +1806,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -1735,10 +1846,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>61</v>
@@ -1750,7 +1861,7 @@
         <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -1771,11 +1882,13 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="77.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1787,7 +1900,8 @@
     <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1808,64 +1922,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>77</v>
@@ -1880,52 +1994,215 @@
         <v>69</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H2" t="s">
+        <v>261</v>
+      </c>
+      <c r="I2" t="s">
+        <v>261</v>
+      </c>
+      <c r="J2" t="s">
+        <v>261</v>
+      </c>
+      <c r="K2" t="s">
+        <v>261</v>
+      </c>
+      <c r="L2" t="s">
+        <v>262</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1478.0</v>
+      </c>
+      <c r="P2" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>106</v>
+      </c>
+      <c r="R2" t="s">
+        <v>176</v>
+      </c>
+      <c r="S2" t="s">
+        <v>288</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1478.0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.2045358325E8</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.2045358325E8</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E3" t="s">
+        <v>289</v>
+      </c>
+      <c r="F3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G3" t="s">
+        <v>290</v>
+      </c>
+      <c r="H3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I3" t="s">
+        <v>261</v>
+      </c>
+      <c r="J3" t="s">
+        <v>261</v>
+      </c>
+      <c r="K3" t="s">
+        <v>261</v>
+      </c>
+      <c r="L3" t="s">
+        <v>262</v>
+      </c>
+      <c r="M3" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="P3" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>106</v>
+      </c>
+      <c r="R3" t="s">
+        <v>188</v>
+      </c>
+      <c r="S3" t="s">
+        <v>291</v>
+      </c>
+      <c r="T3" t="s">
+        <v>292</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3117632.49</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3117632.49</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1977,76 +2254,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2080,19 +2357,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -2113,7 +2390,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2125,16 +2402,114 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.4215213E7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3230730.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8775626.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" t="n">
+        <v>233822.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" t="n">
+        <v>184125.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" t="n">
+        <v>88389.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" t="n">
+        <v>388913.0</v>
       </c>
     </row>
   </sheetData>
@@ -2155,16 +2530,16 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2175,28 +2550,86 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>282</v>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.76435E8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>303</v>
+      </c>
+      <c r="H2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.309E7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H3" t="s">
+        <v>305</v>
+      </c>
+      <c r="I3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J3" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -2217,8 +2650,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2226,27 +2658,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D2" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -2271,8 +2689,8 @@
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="184.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="125.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2289,49 +2707,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="2">
@@ -2339,19 +2757,31 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H2" t="s">
         <v>145</v>
       </c>
-      <c r="C2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="K2" t="s">
         <v>146</v>
       </c>
-      <c r="G2" t="s">
+      <c r="L2" t="s">
         <v>147</v>
-      </c>
-      <c r="M2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="3">
@@ -2362,25 +2792,25 @@
         <v>148</v>
       </c>
       <c r="C3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" t="s">
         <v>149</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>150</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>151</v>
       </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
         <v>152</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>153</v>
-      </c>
-      <c r="H3" t="s">
-        <v>154</v>
-      </c>
-      <c r="J3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="4">
@@ -2388,94 +2818,118 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>154</v>
+      </c>
+      <c r="D4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" t="s">
+        <v>142</v>
       </c>
       <c r="F4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G4" t="s">
-        <v>147</v>
-      </c>
-      <c r="M4" t="s">
-        <v>112</v>
+        <v>155</v>
+      </c>
+      <c r="I4" t="s">
+        <v>152</v>
+      </c>
+      <c r="J4" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="F5" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="G5" t="s">
-        <v>158</v>
-      </c>
-      <c r="I5" t="s">
-        <v>159</v>
-      </c>
-      <c r="J5" t="s">
-        <v>160</v>
+        <v>144</v>
+      </c>
+      <c r="H5" t="s">
+        <v>145</v>
       </c>
       <c r="K5" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="L5" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F6" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H6" t="s">
-        <v>154</v>
+        <v>158</v>
+      </c>
+      <c r="I6" t="s">
+        <v>152</v>
       </c>
       <c r="J6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>154</v>
+      </c>
+      <c r="D7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G7" t="s">
+        <v>155</v>
+      </c>
+      <c r="I7" t="s">
+        <v>152</v>
+      </c>
+      <c r="J7" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2498,12 +2952,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -2535,13 +2989,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="C1" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="D1" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2">
@@ -2549,13 +3003,27 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="C2" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D3" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2578,7 +3046,7 @@
   <cols>
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="30.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2589,22 +3057,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2">
@@ -2615,13 +3083,13 @@
         <v>1.0</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
@@ -2632,13 +3100,13 @@
         <v>2.0</v>
       </c>
       <c r="C3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E3" t="s">
-        <v>120</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4">
@@ -2649,13 +3117,183 @@
         <v>3.0</v>
       </c>
       <c r="C4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" t="s">
         <v>172</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="C6" t="s">
         <v>173</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D6" t="s">
         <v>174</v>
+      </c>
+      <c r="E6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" t="s">
+        <v>176</v>
+      </c>
+      <c r="E7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="C13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="C14" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2691,28 +3329,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2">
@@ -2723,13 +3361,18 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E2" t="s">
-        <v>183</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2753,7 +3396,6 @@
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2762,19 +3404,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2">
@@ -2785,13 +3427,24 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
-      </c>
-      <c r="E2" t="s">
-        <v>189</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2825,22 +3478,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2882,61 +3535,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>60</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -2960,8 +3613,8 @@
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="62.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="66.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2976,7 +3629,8 @@
     <col min="23" max="23" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="32" max="32" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="34" max="34" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3023,58 +3677,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>77</v>
@@ -3086,19 +3740,19 @@
         <v>78</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>71</v>
@@ -3113,25 +3767,25 @@
         <v>64</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>61</v>
@@ -3140,94 +3794,94 @@
         <v>74</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2">
@@ -3238,55 +3892,52 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="D2" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="F2" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="G2" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="H2" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="I2" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="J2" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="K2" t="n">
-        <v>566.0</v>
+        <v>1478.0</v>
       </c>
       <c r="L2" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="M2" t="n">
-        <v>29.0</v>
+        <v>60.0</v>
       </c>
       <c r="T2" t="n">
-        <v>139.65</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.87</v>
+        <v>1478.0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0</v>
+        <v>1.2045358325E8</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0</v>
+        <v>1.2045358325E8</v>
       </c>
       <c r="AB2" t="n">
-        <v>17217.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC2" t="n">
-        <v>837.68</v>
+        <v>0.0</v>
       </c>
       <c r="AF2" t="n">
         <v>0.0</v>
@@ -3304,78 +3955,72 @@
         <v>0.0</v>
       </c>
       <c r="AM2" t="n">
-        <v>837.68</v>
+        <v>0.0</v>
       </c>
       <c r="AN2" t="n">
         <v>0.0</v>
       </c>
-      <c r="AY2" t="s">
-        <v>252</v>
-      </c>
       <c r="BJ2" t="n">
         <v>0.0</v>
       </c>
       <c r="BR2" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="D3" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E3" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="F3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="G3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="H3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="I3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="J3" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="K3" t="n">
-        <v>516.0</v>
+        <v>24.55</v>
       </c>
       <c r="L3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="M3" t="n">
-        <v>27.0</v>
+        <v>1.0</v>
       </c>
       <c r="T3" t="n">
-        <v>127.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.84</v>
+        <v>24.55</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0</v>
+        <v>3117632.49</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0</v>
+        <v>3117632.49</v>
       </c>
       <c r="AB3" t="n">
-        <v>17217.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC3" t="n">
-        <v>763.68</v>
+        <v>0.0</v>
       </c>
       <c r="AF3" t="n">
         <v>0.0</v>
@@ -3393,19 +4038,16 @@
         <v>0.0</v>
       </c>
       <c r="AM3" t="n">
-        <v>763.68</v>
+        <v>0.0</v>
       </c>
       <c r="AN3" t="n">
         <v>0.0</v>
       </c>
-      <c r="AY3" t="s">
-        <v>252</v>
-      </c>
       <c r="BJ3" t="n">
         <v>0.0</v>
       </c>
       <c r="BR3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3451,58 +4093,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
